--- a/consent_forms/013_credit_account_data_usage_consent_form--consent_forms.xlsx
+++ b/consent_forms/013_credit_account_data_usage_consent_form--consent_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1005,12 +1005,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>company_address</t>
+          <t>company_address_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Company Address</t>
+          <t>Company Address 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1032,12 +1032,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>company_website</t>
+          <t>company_website_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Company Website</t>
+          <t>Company Website 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1059,12 +1059,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>data_usage_description</t>
+          <t>data_usage_description_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Data Usage Description</t>
+          <t>Data Usage Description 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>data_retention_period</t>
+          <t>data_retention_period_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Data Retention Period</t>
+          <t>Data Retention Period 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>data_sharing</t>
+          <t>data_sharing_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Data Sharing</t>
+          <t>Data Sharing 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1132,12 +1132,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>contact_person</t>
+          <t>contact_person_2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Contact Person</t>
+          <t>Contact Person 2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1165,9 +1165,9 @@
   <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="31" customWidth="1" min="1" max="1"/>
-    <col width="35" customWidth="1" min="2" max="2"/>
-    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="33" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1195,12 +1195,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_true,_'value':_1}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': True, 'value': 1}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1212,12 +1212,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_false,_'value':_2}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': False, 'value': 2}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1229,12 +1229,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'1_month',_'value':_1}</t>
+          <t>1_month</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': '1 month', 'value': 1}</t>
+          <t>1 month</t>
         </is>
       </c>
     </row>
@@ -1246,12 +1246,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'6_months',_'value':_2}</t>
+          <t>6_months</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': '6 months', 'value': 2}</t>
+          <t>6 months</t>
         </is>
       </c>
     </row>
@@ -1263,12 +1263,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'1_year',_'value':_3}</t>
+          <t>1_year</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': '1 year', 'value': 3}</t>
+          <t>1 year</t>
         </is>
       </c>
     </row>
@@ -1309,58 +1309,58 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>data_retention_period_choices</t>
+          <t>data_retention_period_2_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'1_month',_'value':_1}</t>
+          <t>1_month</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': '1 month', 'value': 1}</t>
+          <t>1 month</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>data_retention_period_choices</t>
+          <t>data_retention_period_2_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'6_months',_'value':_2}</t>
+          <t>6_months</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': '6 months', 'value': 2}</t>
+          <t>6 months</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>data_retention_period_choices</t>
+          <t>data_retention_period_2_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'1_year',_'value':_3}</t>
+          <t>1_year</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': '1 year', 'value': 3}</t>
+          <t>1 year</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>data_sharing_choices</t>
+          <t>data_sharing_2_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1377,7 +1377,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>data_sharing_choices</t>
+          <t>data_sharing_2_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
